--- a/data-raw/vio_mulher.xlsx
+++ b/data-raw/vio_mulher.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projetos de R\Boletim_sdpa\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.rocha\Documents\Projetos R\Boletim_sdpa\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="26">
   <si>
     <t>Sem</t>
   </si>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -166,9 +166,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,7 +206,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
         <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -278,7 +278,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -452,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2068"/>
+  <dimension ref="A1:I2085"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="67.5703125" customWidth="1"/>
@@ -60428,6 +60428,499 @@
       </c>
       <c r="I2068">
         <v>178</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2069">
+        <v>2</v>
+      </c>
+      <c r="B2069">
+        <v>4</v>
+      </c>
+      <c r="C2069">
+        <v>12</v>
+      </c>
+      <c r="D2069">
+        <v>2022</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2069">
+        <v>7</v>
+      </c>
+      <c r="G2069">
+        <v>0</v>
+      </c>
+      <c r="H2069">
+        <v>6</v>
+      </c>
+      <c r="I2069">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2070">
+        <v>2</v>
+      </c>
+      <c r="B2070">
+        <v>4</v>
+      </c>
+      <c r="C2070">
+        <v>12</v>
+      </c>
+      <c r="D2070">
+        <v>2022</v>
+      </c>
+      <c r="E2070" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2070">
+        <v>6</v>
+      </c>
+      <c r="G2070">
+        <v>5</v>
+      </c>
+      <c r="H2070">
+        <v>9</v>
+      </c>
+      <c r="I2070">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2071">
+        <v>2</v>
+      </c>
+      <c r="B2071">
+        <v>4</v>
+      </c>
+      <c r="C2071">
+        <v>12</v>
+      </c>
+      <c r="D2071">
+        <v>2022</v>
+      </c>
+      <c r="E2071" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2071">
+        <v>13</v>
+      </c>
+      <c r="G2071">
+        <v>5</v>
+      </c>
+      <c r="H2071">
+        <v>15</v>
+      </c>
+      <c r="I2071">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2072">
+        <v>2</v>
+      </c>
+      <c r="B2072">
+        <v>4</v>
+      </c>
+      <c r="C2072">
+        <v>12</v>
+      </c>
+      <c r="D2072">
+        <v>2022</v>
+      </c>
+      <c r="E2072" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2072">
+        <v>1</v>
+      </c>
+      <c r="G2072">
+        <v>3</v>
+      </c>
+      <c r="H2072">
+        <v>2</v>
+      </c>
+      <c r="I2072">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2073">
+        <v>2</v>
+      </c>
+      <c r="B2073">
+        <v>4</v>
+      </c>
+      <c r="C2073">
+        <v>12</v>
+      </c>
+      <c r="D2073">
+        <v>2022</v>
+      </c>
+      <c r="E2073" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2073">
+        <v>7</v>
+      </c>
+      <c r="G2073">
+        <v>11</v>
+      </c>
+      <c r="H2073">
+        <v>23</v>
+      </c>
+      <c r="I2073">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2074">
+        <v>2</v>
+      </c>
+      <c r="B2074">
+        <v>4</v>
+      </c>
+      <c r="C2074">
+        <v>12</v>
+      </c>
+      <c r="D2074">
+        <v>2022</v>
+      </c>
+      <c r="E2074" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2074">
+        <v>1660</v>
+      </c>
+      <c r="G2074">
+        <v>741</v>
+      </c>
+      <c r="H2074">
+        <v>2325</v>
+      </c>
+      <c r="I2074">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2075">
+        <v>2</v>
+      </c>
+      <c r="B2075">
+        <v>4</v>
+      </c>
+      <c r="C2075">
+        <v>12</v>
+      </c>
+      <c r="D2075">
+        <v>2022</v>
+      </c>
+      <c r="E2075" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2075">
+        <v>11</v>
+      </c>
+      <c r="G2075">
+        <v>8</v>
+      </c>
+      <c r="H2075">
+        <v>23</v>
+      </c>
+      <c r="I2075">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2076">
+        <v>2</v>
+      </c>
+      <c r="B2076">
+        <v>4</v>
+      </c>
+      <c r="C2076">
+        <v>12</v>
+      </c>
+      <c r="D2076">
+        <v>2022</v>
+      </c>
+      <c r="E2076" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2076">
+        <v>2458</v>
+      </c>
+      <c r="G2076">
+        <v>560</v>
+      </c>
+      <c r="H2076">
+        <v>1999</v>
+      </c>
+      <c r="I2076">
+        <v>5017</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2077">
+        <v>2</v>
+      </c>
+      <c r="B2077">
+        <v>4</v>
+      </c>
+      <c r="C2077">
+        <v>12</v>
+      </c>
+      <c r="D2077">
+        <v>2022</v>
+      </c>
+      <c r="E2077" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2077">
+        <v>24</v>
+      </c>
+      <c r="G2077">
+        <v>12</v>
+      </c>
+      <c r="H2077">
+        <v>74</v>
+      </c>
+      <c r="I2077">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2078">
+        <v>2</v>
+      </c>
+      <c r="B2078">
+        <v>4</v>
+      </c>
+      <c r="C2078">
+        <v>12</v>
+      </c>
+      <c r="D2078">
+        <v>2022</v>
+      </c>
+      <c r="E2078" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2078">
+        <v>2933</v>
+      </c>
+      <c r="G2078">
+        <v>910</v>
+      </c>
+      <c r="H2078">
+        <v>3789</v>
+      </c>
+      <c r="I2078">
+        <v>7632</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2079">
+        <v>2</v>
+      </c>
+      <c r="B2079">
+        <v>4</v>
+      </c>
+      <c r="C2079">
+        <v>12</v>
+      </c>
+      <c r="D2079">
+        <v>2022</v>
+      </c>
+      <c r="E2079" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2079">
+        <v>61</v>
+      </c>
+      <c r="G2079">
+        <v>25</v>
+      </c>
+      <c r="H2079">
+        <v>105</v>
+      </c>
+      <c r="I2079">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2080">
+        <v>2</v>
+      </c>
+      <c r="B2080">
+        <v>4</v>
+      </c>
+      <c r="C2080">
+        <v>12</v>
+      </c>
+      <c r="D2080">
+        <v>2022</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2080">
+        <v>229</v>
+      </c>
+      <c r="G2080">
+        <v>92</v>
+      </c>
+      <c r="H2080">
+        <v>472</v>
+      </c>
+      <c r="I2080">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2081">
+        <v>2</v>
+      </c>
+      <c r="B2081">
+        <v>4</v>
+      </c>
+      <c r="C2081">
+        <v>12</v>
+      </c>
+      <c r="D2081">
+        <v>2022</v>
+      </c>
+      <c r="E2081" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2081">
+        <v>40</v>
+      </c>
+      <c r="G2081">
+        <v>40</v>
+      </c>
+      <c r="H2081">
+        <v>144</v>
+      </c>
+      <c r="I2081">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2082">
+        <v>2</v>
+      </c>
+      <c r="B2082">
+        <v>4</v>
+      </c>
+      <c r="C2082">
+        <v>12</v>
+      </c>
+      <c r="D2082">
+        <v>2022</v>
+      </c>
+      <c r="E2082" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2082">
+        <v>10</v>
+      </c>
+      <c r="G2082">
+        <v>7</v>
+      </c>
+      <c r="H2082">
+        <v>24</v>
+      </c>
+      <c r="I2082">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2083">
+        <v>2</v>
+      </c>
+      <c r="B2083">
+        <v>4</v>
+      </c>
+      <c r="C2083">
+        <v>12</v>
+      </c>
+      <c r="D2083">
+        <v>2022</v>
+      </c>
+      <c r="E2083" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2083">
+        <v>141</v>
+      </c>
+      <c r="G2083">
+        <v>157</v>
+      </c>
+      <c r="H2083">
+        <v>415</v>
+      </c>
+      <c r="I2083">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2084">
+        <v>2</v>
+      </c>
+      <c r="B2084">
+        <v>4</v>
+      </c>
+      <c r="C2084">
+        <v>12</v>
+      </c>
+      <c r="D2084">
+        <v>2022</v>
+      </c>
+      <c r="E2084" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2084">
+        <v>2</v>
+      </c>
+      <c r="G2084">
+        <v>5</v>
+      </c>
+      <c r="H2084">
+        <v>17</v>
+      </c>
+      <c r="I2084">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2085">
+        <v>2</v>
+      </c>
+      <c r="B2085">
+        <v>4</v>
+      </c>
+      <c r="C2085">
+        <v>12</v>
+      </c>
+      <c r="D2085">
+        <v>2022</v>
+      </c>
+      <c r="E2085" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2085">
+        <v>73</v>
+      </c>
+      <c r="G2085">
+        <v>38</v>
+      </c>
+      <c r="H2085">
+        <v>97</v>
+      </c>
+      <c r="I2085">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/vio_mulher.xlsx
+++ b/data-raw/vio_mulher.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.rocha\Documents\Projetos R\Boletim_sdpa\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c945b8f86e4e4dcb/Documentos/Boletim_sdpa/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_C182D1E83937D3F556BD82D774E7EED3926440D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81E1129E-90AA-4EA1-9DCF-467F0C5243C8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="26">
   <si>
     <t>Sem</t>
   </si>
@@ -105,7 +106,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -143,10 +144,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -166,9 +174,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,9 +214,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -243,7 +251,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -278,7 +286,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -451,8 +459,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2085"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J2205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="67.5703125" customWidth="1"/>
@@ -60778,7 +60786,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="2081" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2081" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2081">
         <v>2</v>
       </c>
@@ -60807,7 +60815,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2082" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2082" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2082">
         <v>2</v>
       </c>
@@ -60836,7 +60844,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2083" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2083" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2083">
         <v>2</v>
       </c>
@@ -60865,7 +60873,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="2084" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2084" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2084">
         <v>2</v>
       </c>
@@ -60894,7 +60902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2085" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2085" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2085">
         <v>2</v>
       </c>
@@ -60907,25 +60915,3603 @@
       <c r="D2085">
         <v>2022</v>
       </c>
-      <c r="E2085" t="s">
+      <c r="E2085" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2085">
+      <c r="F2085" s="3">
         <v>73</v>
       </c>
-      <c r="G2085">
+      <c r="G2085" s="3">
         <v>38</v>
       </c>
-      <c r="H2085">
+      <c r="H2085" s="3">
         <v>97</v>
       </c>
-      <c r="I2085">
+      <c r="I2085" s="3">
         <v>208</v>
       </c>
+      <c r="J2085" s="2"/>
+    </row>
+    <row r="2086" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2086">
+        <v>1</v>
+      </c>
+      <c r="B2086">
+        <v>1</v>
+      </c>
+      <c r="C2086">
+        <v>1</v>
+      </c>
+      <c r="D2086">
+        <v>2023</v>
+      </c>
+      <c r="E2086" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2086" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2086" s="6">
+        <v>9</v>
+      </c>
+      <c r="H2086" s="6">
+        <v>9</v>
+      </c>
+      <c r="I2086" s="4">
+        <v>20</v>
+      </c>
+      <c r="J2086" s="2"/>
+    </row>
+    <row r="2087" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2087">
+        <v>1</v>
+      </c>
+      <c r="B2087">
+        <v>1</v>
+      </c>
+      <c r="C2087">
+        <v>1</v>
+      </c>
+      <c r="D2087">
+        <v>2023</v>
+      </c>
+      <c r="E2087" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2087" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2087" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2087" s="6">
+        <v>16</v>
+      </c>
+      <c r="I2087" s="6">
+        <v>18</v>
+      </c>
+      <c r="J2087" s="2"/>
+    </row>
+    <row r="2088" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2088">
+        <v>1</v>
+      </c>
+      <c r="B2088">
+        <v>1</v>
+      </c>
+      <c r="C2088">
+        <v>1</v>
+      </c>
+      <c r="D2088">
+        <v>2023</v>
+      </c>
+      <c r="E2088" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2088" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2088" s="6">
+        <v>11</v>
+      </c>
+      <c r="H2088" s="6">
+        <v>25</v>
+      </c>
+      <c r="I2088" s="6">
+        <v>38</v>
+      </c>
+      <c r="J2088" s="2"/>
+    </row>
+    <row r="2089" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2089">
+        <v>1</v>
+      </c>
+      <c r="B2089">
+        <v>1</v>
+      </c>
+      <c r="C2089">
+        <v>1</v>
+      </c>
+      <c r="D2089">
+        <v>2023</v>
+      </c>
+      <c r="E2089" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2089" s="6">
+        <v>6</v>
+      </c>
+      <c r="G2089" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2089" s="6">
+        <v>4</v>
+      </c>
+      <c r="I2089" s="6">
+        <v>13</v>
+      </c>
+      <c r="J2089" s="2"/>
+    </row>
+    <row r="2090" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2090">
+        <v>1</v>
+      </c>
+      <c r="B2090">
+        <v>1</v>
+      </c>
+      <c r="C2090">
+        <v>1</v>
+      </c>
+      <c r="D2090">
+        <v>2023</v>
+      </c>
+      <c r="E2090" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2090" s="6">
+        <v>6</v>
+      </c>
+      <c r="G2090" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2090" s="6">
+        <v>21</v>
+      </c>
+      <c r="I2090" s="6">
+        <v>34</v>
+      </c>
+      <c r="J2090" s="2"/>
+    </row>
+    <row r="2091" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2091">
+        <v>1</v>
+      </c>
+      <c r="B2091">
+        <v>1</v>
+      </c>
+      <c r="C2091">
+        <v>1</v>
+      </c>
+      <c r="D2091">
+        <v>2023</v>
+      </c>
+      <c r="E2091" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2091" s="6">
+        <v>1748</v>
+      </c>
+      <c r="G2091" s="6">
+        <v>804</v>
+      </c>
+      <c r="H2091" s="6">
+        <v>2416</v>
+      </c>
+      <c r="I2091" s="6">
+        <v>4968</v>
+      </c>
+      <c r="J2091" s="2"/>
+    </row>
+    <row r="2092" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2092">
+        <v>1</v>
+      </c>
+      <c r="B2092">
+        <v>1</v>
+      </c>
+      <c r="C2092">
+        <v>1</v>
+      </c>
+      <c r="D2092">
+        <v>2023</v>
+      </c>
+      <c r="E2092" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2092" s="6">
+        <v>14</v>
+      </c>
+      <c r="G2092" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2092" s="6">
+        <v>26</v>
+      </c>
+      <c r="I2092" s="6">
+        <v>47</v>
+      </c>
+      <c r="J2092" s="2"/>
+    </row>
+    <row r="2093" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2093">
+        <v>1</v>
+      </c>
+      <c r="B2093">
+        <v>1</v>
+      </c>
+      <c r="C2093">
+        <v>1</v>
+      </c>
+      <c r="D2093">
+        <v>2023</v>
+      </c>
+      <c r="E2093" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2093" s="6">
+        <v>2686</v>
+      </c>
+      <c r="G2093" s="6">
+        <v>623</v>
+      </c>
+      <c r="H2093" s="6">
+        <v>2437</v>
+      </c>
+      <c r="I2093" s="6">
+        <v>5746</v>
+      </c>
+      <c r="J2093" s="2"/>
+    </row>
+    <row r="2094" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2094">
+        <v>1</v>
+      </c>
+      <c r="B2094">
+        <v>1</v>
+      </c>
+      <c r="C2094">
+        <v>1</v>
+      </c>
+      <c r="D2094">
+        <v>2023</v>
+      </c>
+      <c r="E2094" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2094" s="6">
+        <v>27</v>
+      </c>
+      <c r="G2094" s="6">
+        <v>10</v>
+      </c>
+      <c r="H2094" s="6">
+        <v>91</v>
+      </c>
+      <c r="I2094" s="6">
+        <v>128</v>
+      </c>
+      <c r="J2094" s="2"/>
+    </row>
+    <row r="2095" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2095">
+        <v>1</v>
+      </c>
+      <c r="B2095">
+        <v>1</v>
+      </c>
+      <c r="C2095">
+        <v>1</v>
+      </c>
+      <c r="D2095">
+        <v>2023</v>
+      </c>
+      <c r="E2095" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2095" s="6">
+        <v>3230</v>
+      </c>
+      <c r="G2095" s="6">
+        <v>1063</v>
+      </c>
+      <c r="H2095" s="6">
+        <v>4208</v>
+      </c>
+      <c r="I2095" s="6">
+        <v>8501</v>
+      </c>
+      <c r="J2095" s="2"/>
+    </row>
+    <row r="2096" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2096">
+        <v>1</v>
+      </c>
+      <c r="B2096">
+        <v>1</v>
+      </c>
+      <c r="C2096">
+        <v>1</v>
+      </c>
+      <c r="D2096">
+        <v>2023</v>
+      </c>
+      <c r="E2096" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2096" s="6">
+        <v>51</v>
+      </c>
+      <c r="G2096" s="6">
+        <v>24</v>
+      </c>
+      <c r="H2096" s="6">
+        <v>120</v>
+      </c>
+      <c r="I2096" s="6">
+        <v>195</v>
+      </c>
+      <c r="J2096" s="2"/>
+    </row>
+    <row r="2097" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2097">
+        <v>1</v>
+      </c>
+      <c r="B2097">
+        <v>1</v>
+      </c>
+      <c r="C2097">
+        <v>1</v>
+      </c>
+      <c r="D2097">
+        <v>2023</v>
+      </c>
+      <c r="E2097" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2097" s="6">
+        <v>201</v>
+      </c>
+      <c r="G2097" s="6">
+        <v>99</v>
+      </c>
+      <c r="H2097" s="6">
+        <v>516</v>
+      </c>
+      <c r="I2097" s="6">
+        <v>816</v>
+      </c>
+      <c r="J2097" s="2"/>
+    </row>
+    <row r="2098" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2098">
+        <v>1</v>
+      </c>
+      <c r="B2098">
+        <v>1</v>
+      </c>
+      <c r="C2098">
+        <v>1</v>
+      </c>
+      <c r="D2098">
+        <v>2023</v>
+      </c>
+      <c r="E2098" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2098" s="6">
+        <v>28</v>
+      </c>
+      <c r="G2098" s="6">
+        <v>20</v>
+      </c>
+      <c r="H2098" s="6">
+        <v>86</v>
+      </c>
+      <c r="I2098" s="6">
+        <v>134</v>
+      </c>
+      <c r="J2098" s="2"/>
+    </row>
+    <row r="2099" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2099">
+        <v>1</v>
+      </c>
+      <c r="B2099">
+        <v>1</v>
+      </c>
+      <c r="C2099">
+        <v>1</v>
+      </c>
+      <c r="D2099">
+        <v>2023</v>
+      </c>
+      <c r="E2099" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2099" s="6">
+        <v>13</v>
+      </c>
+      <c r="G2099" s="6">
+        <v>6</v>
+      </c>
+      <c r="H2099" s="6">
+        <v>28</v>
+      </c>
+      <c r="I2099" s="6">
+        <v>47</v>
+      </c>
+      <c r="J2099" s="2"/>
+    </row>
+    <row r="2100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2100">
+        <v>1</v>
+      </c>
+      <c r="B2100">
+        <v>1</v>
+      </c>
+      <c r="C2100">
+        <v>1</v>
+      </c>
+      <c r="D2100">
+        <v>2023</v>
+      </c>
+      <c r="E2100" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2100" s="6">
+        <v>81</v>
+      </c>
+      <c r="G2100" s="6">
+        <v>52</v>
+      </c>
+      <c r="H2100" s="6">
+        <v>204</v>
+      </c>
+      <c r="I2100" s="6">
+        <v>337</v>
+      </c>
+      <c r="J2100" s="2"/>
+    </row>
+    <row r="2101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2101">
+        <v>1</v>
+      </c>
+      <c r="B2101">
+        <v>1</v>
+      </c>
+      <c r="C2101">
+        <v>1</v>
+      </c>
+      <c r="D2101">
+        <v>2023</v>
+      </c>
+      <c r="E2101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2101" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2101" s="6">
+        <v>4</v>
+      </c>
+      <c r="H2101" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2101" s="6">
+        <v>17</v>
+      </c>
+      <c r="J2101" s="2"/>
+    </row>
+    <row r="2102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2102">
+        <v>1</v>
+      </c>
+      <c r="B2102">
+        <v>1</v>
+      </c>
+      <c r="C2102">
+        <v>1</v>
+      </c>
+      <c r="D2102">
+        <v>2023</v>
+      </c>
+      <c r="E2102" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2102" s="6">
+        <v>81</v>
+      </c>
+      <c r="G2102" s="6">
+        <v>35</v>
+      </c>
+      <c r="H2102" s="6">
+        <v>120</v>
+      </c>
+      <c r="I2102" s="6">
+        <v>236</v>
+      </c>
+      <c r="J2102" s="2"/>
+    </row>
+    <row r="2103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2103">
+        <v>1</v>
+      </c>
+      <c r="B2103">
+        <v>1</v>
+      </c>
+      <c r="C2103">
+        <v>2</v>
+      </c>
+      <c r="D2103">
+        <v>2023</v>
+      </c>
+      <c r="E2103" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2103" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2103" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2103" s="6">
+        <v>10</v>
+      </c>
+      <c r="I2103" s="6">
+        <v>22</v>
+      </c>
+      <c r="J2103" s="2"/>
+    </row>
+    <row r="2104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2104">
+        <v>1</v>
+      </c>
+      <c r="B2104">
+        <v>1</v>
+      </c>
+      <c r="C2104">
+        <v>2</v>
+      </c>
+      <c r="D2104">
+        <v>2023</v>
+      </c>
+      <c r="E2104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2104" s="6">
+        <v>4</v>
+      </c>
+      <c r="G2104" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2104" s="6">
+        <v>18</v>
+      </c>
+      <c r="I2104" s="6">
+        <v>25</v>
+      </c>
+      <c r="J2104" s="2"/>
+    </row>
+    <row r="2105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2105">
+        <v>1</v>
+      </c>
+      <c r="B2105">
+        <v>1</v>
+      </c>
+      <c r="C2105">
+        <v>2</v>
+      </c>
+      <c r="D2105">
+        <v>2023</v>
+      </c>
+      <c r="E2105" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2105" s="6">
+        <v>9</v>
+      </c>
+      <c r="G2105" s="6">
+        <v>10</v>
+      </c>
+      <c r="H2105" s="6">
+        <v>28</v>
+      </c>
+      <c r="I2105" s="6">
+        <v>47</v>
+      </c>
+      <c r="J2105" s="2"/>
+    </row>
+    <row r="2106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2106">
+        <v>1</v>
+      </c>
+      <c r="B2106">
+        <v>1</v>
+      </c>
+      <c r="C2106">
+        <v>2</v>
+      </c>
+      <c r="D2106">
+        <v>2023</v>
+      </c>
+      <c r="E2106" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2106" s="6">
+        <v>3</v>
+      </c>
+      <c r="G2106" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2106" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2106" s="6">
+        <v>12</v>
+      </c>
+      <c r="J2106" s="2"/>
+    </row>
+    <row r="2107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2107">
+        <v>1</v>
+      </c>
+      <c r="B2107">
+        <v>1</v>
+      </c>
+      <c r="C2107">
+        <v>2</v>
+      </c>
+      <c r="D2107">
+        <v>2023</v>
+      </c>
+      <c r="E2107" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2107" s="6">
+        <v>12</v>
+      </c>
+      <c r="G2107" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2107" s="6">
+        <v>16</v>
+      </c>
+      <c r="I2107" s="6">
+        <v>35</v>
+      </c>
+      <c r="J2107" s="2"/>
+    </row>
+    <row r="2108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2108">
+        <v>1</v>
+      </c>
+      <c r="B2108">
+        <v>1</v>
+      </c>
+      <c r="C2108">
+        <v>2</v>
+      </c>
+      <c r="D2108">
+        <v>2023</v>
+      </c>
+      <c r="E2108" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2108" s="6">
+        <v>1660</v>
+      </c>
+      <c r="G2108" s="6">
+        <v>712</v>
+      </c>
+      <c r="H2108" s="6">
+        <v>2303</v>
+      </c>
+      <c r="I2108" s="6">
+        <v>4675</v>
+      </c>
+      <c r="J2108" s="2"/>
+    </row>
+    <row r="2109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2109">
+        <v>1</v>
+      </c>
+      <c r="B2109">
+        <v>1</v>
+      </c>
+      <c r="C2109">
+        <v>2</v>
+      </c>
+      <c r="D2109">
+        <v>2023</v>
+      </c>
+      <c r="E2109" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2109" s="6">
+        <v>11</v>
+      </c>
+      <c r="G2109" s="6">
+        <v>6</v>
+      </c>
+      <c r="H2109" s="6">
+        <v>23</v>
+      </c>
+      <c r="I2109" s="6">
+        <v>40</v>
+      </c>
+      <c r="J2109" s="2"/>
+    </row>
+    <row r="2110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2110">
+        <v>1</v>
+      </c>
+      <c r="B2110">
+        <v>1</v>
+      </c>
+      <c r="C2110">
+        <v>2</v>
+      </c>
+      <c r="D2110">
+        <v>2023</v>
+      </c>
+      <c r="E2110" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2110" s="6">
+        <v>2390</v>
+      </c>
+      <c r="G2110" s="6">
+        <v>615</v>
+      </c>
+      <c r="H2110" s="6">
+        <v>2206</v>
+      </c>
+      <c r="I2110" s="6">
+        <v>5211</v>
+      </c>
+      <c r="J2110" s="2"/>
+    </row>
+    <row r="2111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2111">
+        <v>1</v>
+      </c>
+      <c r="B2111">
+        <v>1</v>
+      </c>
+      <c r="C2111">
+        <v>2</v>
+      </c>
+      <c r="D2111">
+        <v>2023</v>
+      </c>
+      <c r="E2111" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2111" s="6">
+        <v>16</v>
+      </c>
+      <c r="G2111" s="6">
+        <v>16</v>
+      </c>
+      <c r="H2111" s="6">
+        <v>74</v>
+      </c>
+      <c r="I2111" s="6">
+        <v>106</v>
+      </c>
+      <c r="J2111" s="2"/>
+    </row>
+    <row r="2112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2112">
+        <v>1</v>
+      </c>
+      <c r="B2112">
+        <v>1</v>
+      </c>
+      <c r="C2112">
+        <v>2</v>
+      </c>
+      <c r="D2112">
+        <v>2023</v>
+      </c>
+      <c r="E2112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2112" s="6">
+        <v>2917</v>
+      </c>
+      <c r="G2112" s="6">
+        <v>973</v>
+      </c>
+      <c r="H2112" s="6">
+        <v>3870</v>
+      </c>
+      <c r="I2112" s="6">
+        <v>7760</v>
+      </c>
+      <c r="J2112" s="2"/>
+    </row>
+    <row r="2113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2113">
+        <v>1</v>
+      </c>
+      <c r="B2113">
+        <v>1</v>
+      </c>
+      <c r="C2113">
+        <v>2</v>
+      </c>
+      <c r="D2113">
+        <v>2023</v>
+      </c>
+      <c r="E2113" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2113" s="6">
+        <v>63</v>
+      </c>
+      <c r="G2113" s="6">
+        <v>25</v>
+      </c>
+      <c r="H2113" s="6">
+        <v>95</v>
+      </c>
+      <c r="I2113" s="6">
+        <v>183</v>
+      </c>
+      <c r="J2113" s="2"/>
+    </row>
+    <row r="2114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2114">
+        <v>1</v>
+      </c>
+      <c r="B2114">
+        <v>1</v>
+      </c>
+      <c r="C2114">
+        <v>2</v>
+      </c>
+      <c r="D2114">
+        <v>2023</v>
+      </c>
+      <c r="E2114" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2114" s="6">
+        <v>216</v>
+      </c>
+      <c r="G2114" s="6">
+        <v>100</v>
+      </c>
+      <c r="H2114" s="6">
+        <v>461</v>
+      </c>
+      <c r="I2114" s="6">
+        <v>777</v>
+      </c>
+      <c r="J2114" s="2"/>
+    </row>
+    <row r="2115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2115">
+        <v>1</v>
+      </c>
+      <c r="B2115">
+        <v>1</v>
+      </c>
+      <c r="C2115">
+        <v>2</v>
+      </c>
+      <c r="D2115">
+        <v>2023</v>
+      </c>
+      <c r="E2115" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2115" s="6">
+        <v>52</v>
+      </c>
+      <c r="G2115" s="6">
+        <v>42</v>
+      </c>
+      <c r="H2115" s="6">
+        <v>108</v>
+      </c>
+      <c r="I2115" s="6">
+        <v>202</v>
+      </c>
+      <c r="J2115" s="2"/>
+    </row>
+    <row r="2116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2116">
+        <v>1</v>
+      </c>
+      <c r="B2116">
+        <v>1</v>
+      </c>
+      <c r="C2116">
+        <v>2</v>
+      </c>
+      <c r="D2116">
+        <v>2023</v>
+      </c>
+      <c r="E2116" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2116" s="6">
+        <v>10</v>
+      </c>
+      <c r="G2116" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2116" s="6">
+        <v>20</v>
+      </c>
+      <c r="I2116" s="6">
+        <v>37</v>
+      </c>
+      <c r="J2116" s="2"/>
+    </row>
+    <row r="2117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2117">
+        <v>1</v>
+      </c>
+      <c r="B2117">
+        <v>1</v>
+      </c>
+      <c r="C2117">
+        <v>2</v>
+      </c>
+      <c r="D2117">
+        <v>2023</v>
+      </c>
+      <c r="E2117" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2117" s="6">
+        <v>130</v>
+      </c>
+      <c r="G2117" s="6">
+        <v>87</v>
+      </c>
+      <c r="H2117" s="6">
+        <v>315</v>
+      </c>
+      <c r="I2117" s="6">
+        <v>532</v>
+      </c>
+      <c r="J2117" s="2"/>
+    </row>
+    <row r="2118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2118">
+        <v>1</v>
+      </c>
+      <c r="B2118">
+        <v>1</v>
+      </c>
+      <c r="C2118">
+        <v>2</v>
+      </c>
+      <c r="D2118">
+        <v>2023</v>
+      </c>
+      <c r="E2118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2118" s="6">
+        <v>3</v>
+      </c>
+      <c r="G2118" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2118" s="6">
+        <v>5</v>
+      </c>
+      <c r="I2118" s="6">
+        <v>10</v>
+      </c>
+      <c r="J2118" s="2"/>
+    </row>
+    <row r="2119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2119">
+        <v>1</v>
+      </c>
+      <c r="B2119">
+        <v>1</v>
+      </c>
+      <c r="C2119">
+        <v>2</v>
+      </c>
+      <c r="D2119">
+        <v>2023</v>
+      </c>
+      <c r="E2119" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2119" s="6">
+        <v>76</v>
+      </c>
+      <c r="G2119" s="6">
+        <v>38</v>
+      </c>
+      <c r="H2119" s="6">
+        <v>89</v>
+      </c>
+      <c r="I2119" s="6">
+        <v>203</v>
+      </c>
+      <c r="J2119" s="2"/>
+    </row>
+    <row r="2120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2120">
+        <v>1</v>
+      </c>
+      <c r="B2120">
+        <v>1</v>
+      </c>
+      <c r="C2120">
+        <v>3</v>
+      </c>
+      <c r="D2120">
+        <v>2023</v>
+      </c>
+      <c r="E2120" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2120" s="6">
+        <v>4</v>
+      </c>
+      <c r="G2120" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2120" s="6">
+        <v>14</v>
+      </c>
+      <c r="I2120" s="6">
+        <v>25</v>
+      </c>
+      <c r="J2120" s="2"/>
+    </row>
+    <row r="2121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2121">
+        <v>1</v>
+      </c>
+      <c r="B2121">
+        <v>1</v>
+      </c>
+      <c r="C2121">
+        <v>3</v>
+      </c>
+      <c r="D2121">
+        <v>2023</v>
+      </c>
+      <c r="E2121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2121" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2121" s="6">
+        <v>4</v>
+      </c>
+      <c r="H2121" s="6">
+        <v>12</v>
+      </c>
+      <c r="I2121" s="6">
+        <v>18</v>
+      </c>
+      <c r="J2121" s="2"/>
+    </row>
+    <row r="2122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2122">
+        <v>1</v>
+      </c>
+      <c r="B2122">
+        <v>1</v>
+      </c>
+      <c r="C2122">
+        <v>3</v>
+      </c>
+      <c r="D2122">
+        <v>2023</v>
+      </c>
+      <c r="E2122" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2122" s="6">
+        <v>6</v>
+      </c>
+      <c r="G2122" s="6">
+        <v>11</v>
+      </c>
+      <c r="H2122" s="6">
+        <v>26</v>
+      </c>
+      <c r="I2122" s="6">
+        <v>43</v>
+      </c>
+      <c r="J2122" s="2"/>
+    </row>
+    <row r="2123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2123">
+        <v>1</v>
+      </c>
+      <c r="B2123">
+        <v>1</v>
+      </c>
+      <c r="C2123">
+        <v>3</v>
+      </c>
+      <c r="D2123">
+        <v>2023</v>
+      </c>
+      <c r="E2123" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2123" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2123" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2123" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2123" s="6">
+        <v>13</v>
+      </c>
+      <c r="J2123" s="2"/>
+    </row>
+    <row r="2124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2124">
+        <v>1</v>
+      </c>
+      <c r="B2124">
+        <v>1</v>
+      </c>
+      <c r="C2124">
+        <v>3</v>
+      </c>
+      <c r="D2124">
+        <v>2023</v>
+      </c>
+      <c r="E2124" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2124" s="6">
+        <v>4</v>
+      </c>
+      <c r="G2124" s="6">
+        <v>10</v>
+      </c>
+      <c r="H2124" s="6">
+        <v>18</v>
+      </c>
+      <c r="I2124" s="6">
+        <v>32</v>
+      </c>
+      <c r="J2124" s="2"/>
+    </row>
+    <row r="2125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2125">
+        <v>1</v>
+      </c>
+      <c r="B2125">
+        <v>1</v>
+      </c>
+      <c r="C2125">
+        <v>3</v>
+      </c>
+      <c r="D2125">
+        <v>2023</v>
+      </c>
+      <c r="E2125" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2125" s="6">
+        <v>1860</v>
+      </c>
+      <c r="G2125" s="6">
+        <v>796</v>
+      </c>
+      <c r="H2125" s="6">
+        <v>2624</v>
+      </c>
+      <c r="I2125" s="6">
+        <v>5280</v>
+      </c>
+      <c r="J2125" s="2"/>
+    </row>
+    <row r="2126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2126">
+        <v>1</v>
+      </c>
+      <c r="B2126">
+        <v>1</v>
+      </c>
+      <c r="C2126">
+        <v>3</v>
+      </c>
+      <c r="D2126">
+        <v>2023</v>
+      </c>
+      <c r="E2126" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2126" s="6">
+        <v>20</v>
+      </c>
+      <c r="G2126" s="6">
+        <v>12</v>
+      </c>
+      <c r="H2126" s="6">
+        <v>42</v>
+      </c>
+      <c r="I2126" s="6">
+        <v>74</v>
+      </c>
+      <c r="J2126" s="2"/>
+    </row>
+    <row r="2127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2127">
+        <v>1</v>
+      </c>
+      <c r="B2127">
+        <v>1</v>
+      </c>
+      <c r="C2127">
+        <v>3</v>
+      </c>
+      <c r="D2127">
+        <v>2023</v>
+      </c>
+      <c r="E2127" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2127" s="6">
+        <v>2769</v>
+      </c>
+      <c r="G2127" s="6">
+        <v>752</v>
+      </c>
+      <c r="H2127" s="6">
+        <v>2730</v>
+      </c>
+      <c r="I2127" s="6">
+        <v>6251</v>
+      </c>
+      <c r="J2127" s="2"/>
+    </row>
+    <row r="2128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2128">
+        <v>1</v>
+      </c>
+      <c r="B2128">
+        <v>1</v>
+      </c>
+      <c r="C2128">
+        <v>3</v>
+      </c>
+      <c r="D2128">
+        <v>2023</v>
+      </c>
+      <c r="E2128" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2128" s="6">
+        <v>21</v>
+      </c>
+      <c r="G2128" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2128" s="6">
+        <v>50</v>
+      </c>
+      <c r="I2128" s="6">
+        <v>76</v>
+      </c>
+      <c r="J2128" s="2"/>
+    </row>
+    <row r="2129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2129">
+        <v>1</v>
+      </c>
+      <c r="B2129">
+        <v>1</v>
+      </c>
+      <c r="C2129">
+        <v>3</v>
+      </c>
+      <c r="D2129">
+        <v>2023</v>
+      </c>
+      <c r="E2129" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2129" s="6">
+        <v>3421</v>
+      </c>
+      <c r="G2129" s="6">
+        <v>1156</v>
+      </c>
+      <c r="H2129" s="6">
+        <v>4693</v>
+      </c>
+      <c r="I2129" s="6">
+        <v>9270</v>
+      </c>
+      <c r="J2129" s="2"/>
+    </row>
+    <row r="2130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2130">
+        <v>1</v>
+      </c>
+      <c r="B2130">
+        <v>1</v>
+      </c>
+      <c r="C2130">
+        <v>3</v>
+      </c>
+      <c r="D2130">
+        <v>2023</v>
+      </c>
+      <c r="E2130" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2130" s="6">
+        <v>66</v>
+      </c>
+      <c r="G2130" s="6">
+        <v>28</v>
+      </c>
+      <c r="H2130" s="6">
+        <v>117</v>
+      </c>
+      <c r="I2130" s="6">
+        <v>211</v>
+      </c>
+      <c r="J2130" s="2"/>
+    </row>
+    <row r="2131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2131">
+        <v>1</v>
+      </c>
+      <c r="B2131">
+        <v>1</v>
+      </c>
+      <c r="C2131">
+        <v>3</v>
+      </c>
+      <c r="D2131">
+        <v>2023</v>
+      </c>
+      <c r="E2131" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2131" s="6">
+        <v>207</v>
+      </c>
+      <c r="G2131" s="6">
+        <v>121</v>
+      </c>
+      <c r="H2131" s="6">
+        <v>522</v>
+      </c>
+      <c r="I2131" s="6">
+        <v>850</v>
+      </c>
+      <c r="J2131" s="2"/>
+    </row>
+    <row r="2132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2132">
+        <v>1</v>
+      </c>
+      <c r="B2132">
+        <v>1</v>
+      </c>
+      <c r="C2132">
+        <v>3</v>
+      </c>
+      <c r="D2132">
+        <v>2023</v>
+      </c>
+      <c r="E2132" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2132" s="6">
+        <v>59</v>
+      </c>
+      <c r="G2132" s="6">
+        <v>52</v>
+      </c>
+      <c r="H2132" s="6">
+        <v>174</v>
+      </c>
+      <c r="I2132" s="6">
+        <v>285</v>
+      </c>
+      <c r="J2132" s="2"/>
+    </row>
+    <row r="2133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2133">
+        <v>1</v>
+      </c>
+      <c r="B2133">
+        <v>1</v>
+      </c>
+      <c r="C2133">
+        <v>3</v>
+      </c>
+      <c r="D2133">
+        <v>2023</v>
+      </c>
+      <c r="E2133" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2133" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2133" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2133" s="6">
+        <v>27</v>
+      </c>
+      <c r="I2133" s="6">
+        <v>39</v>
+      </c>
+      <c r="J2133" s="2"/>
+    </row>
+    <row r="2134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2134">
+        <v>1</v>
+      </c>
+      <c r="B2134">
+        <v>1</v>
+      </c>
+      <c r="C2134">
+        <v>3</v>
+      </c>
+      <c r="D2134">
+        <v>2023</v>
+      </c>
+      <c r="E2134" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2134" s="6">
+        <v>194</v>
+      </c>
+      <c r="G2134" s="6">
+        <v>215</v>
+      </c>
+      <c r="H2134" s="6">
+        <v>546</v>
+      </c>
+      <c r="I2134" s="6">
+        <v>955</v>
+      </c>
+      <c r="J2134" s="2"/>
+    </row>
+    <row r="2135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2135">
+        <v>1</v>
+      </c>
+      <c r="B2135">
+        <v>1</v>
+      </c>
+      <c r="C2135">
+        <v>3</v>
+      </c>
+      <c r="D2135">
+        <v>2023</v>
+      </c>
+      <c r="E2135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2135" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2135" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2135" s="6">
+        <v>12</v>
+      </c>
+      <c r="I2135" s="6">
+        <v>16</v>
+      </c>
+      <c r="J2135" s="2"/>
+    </row>
+    <row r="2136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2136">
+        <v>1</v>
+      </c>
+      <c r="B2136">
+        <v>1</v>
+      </c>
+      <c r="C2136">
+        <v>3</v>
+      </c>
+      <c r="D2136">
+        <v>2023</v>
+      </c>
+      <c r="E2136" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2136" s="6">
+        <v>94</v>
+      </c>
+      <c r="G2136" s="6">
+        <v>55</v>
+      </c>
+      <c r="H2136" s="6">
+        <v>130</v>
+      </c>
+      <c r="I2136" s="6">
+        <v>279</v>
+      </c>
+      <c r="J2136" s="2"/>
+    </row>
+    <row r="2137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2137">
+        <v>1</v>
+      </c>
+      <c r="B2137">
+        <v>2</v>
+      </c>
+      <c r="C2137">
+        <v>4</v>
+      </c>
+      <c r="D2137">
+        <v>2023</v>
+      </c>
+      <c r="E2137" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2137" s="6">
+        <v>6</v>
+      </c>
+      <c r="G2137" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2137" s="6">
+        <v>11</v>
+      </c>
+      <c r="I2137" s="6">
+        <v>19</v>
+      </c>
+      <c r="J2137" s="2"/>
+    </row>
+    <row r="2138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2138">
+        <v>1</v>
+      </c>
+      <c r="B2138">
+        <v>2</v>
+      </c>
+      <c r="C2138">
+        <v>4</v>
+      </c>
+      <c r="D2138">
+        <v>2023</v>
+      </c>
+      <c r="E2138" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2138" s="6">
+        <v>7</v>
+      </c>
+      <c r="G2138" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2138" s="6">
+        <v>9</v>
+      </c>
+      <c r="I2138" s="6">
+        <v>19</v>
+      </c>
+      <c r="J2138" s="2"/>
+    </row>
+    <row r="2139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2139">
+        <v>1</v>
+      </c>
+      <c r="B2139">
+        <v>2</v>
+      </c>
+      <c r="C2139">
+        <v>4</v>
+      </c>
+      <c r="D2139">
+        <v>2023</v>
+      </c>
+      <c r="E2139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2139" s="6">
+        <v>13</v>
+      </c>
+      <c r="G2139" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2139" s="6">
+        <v>20</v>
+      </c>
+      <c r="I2139" s="6">
+        <v>38</v>
+      </c>
+      <c r="J2139" s="2"/>
+    </row>
+    <row r="2140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2140">
+        <v>1</v>
+      </c>
+      <c r="B2140">
+        <v>2</v>
+      </c>
+      <c r="C2140">
+        <v>4</v>
+      </c>
+      <c r="D2140">
+        <v>2023</v>
+      </c>
+      <c r="E2140" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2140" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2140" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2140" s="6">
+        <v>5</v>
+      </c>
+      <c r="I2140" s="6">
+        <v>8</v>
+      </c>
+      <c r="J2140" s="2"/>
+    </row>
+    <row r="2141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2141">
+        <v>1</v>
+      </c>
+      <c r="B2141">
+        <v>2</v>
+      </c>
+      <c r="C2141">
+        <v>4</v>
+      </c>
+      <c r="D2141">
+        <v>2023</v>
+      </c>
+      <c r="E2141" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2141" s="6">
+        <v>3</v>
+      </c>
+      <c r="G2141" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2141" s="6">
+        <v>18</v>
+      </c>
+      <c r="I2141" s="6">
+        <v>26</v>
+      </c>
+      <c r="J2141" s="2"/>
+    </row>
+    <row r="2142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2142">
+        <v>1</v>
+      </c>
+      <c r="B2142">
+        <v>2</v>
+      </c>
+      <c r="C2142">
+        <v>4</v>
+      </c>
+      <c r="D2142">
+        <v>2023</v>
+      </c>
+      <c r="E2142" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2142" s="6">
+        <v>1726</v>
+      </c>
+      <c r="G2142" s="6">
+        <v>640</v>
+      </c>
+      <c r="H2142" s="6">
+        <v>2198</v>
+      </c>
+      <c r="I2142" s="6">
+        <v>4564</v>
+      </c>
+      <c r="J2142" s="2"/>
+    </row>
+    <row r="2143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2143">
+        <v>1</v>
+      </c>
+      <c r="B2143">
+        <v>2</v>
+      </c>
+      <c r="C2143">
+        <v>4</v>
+      </c>
+      <c r="D2143">
+        <v>2023</v>
+      </c>
+      <c r="E2143" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2143" s="6">
+        <v>8</v>
+      </c>
+      <c r="G2143" s="6">
+        <v>10</v>
+      </c>
+      <c r="H2143" s="6">
+        <v>31</v>
+      </c>
+      <c r="I2143" s="6">
+        <v>49</v>
+      </c>
+      <c r="J2143" s="2"/>
+    </row>
+    <row r="2144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2144">
+        <v>1</v>
+      </c>
+      <c r="B2144">
+        <v>2</v>
+      </c>
+      <c r="C2144">
+        <v>4</v>
+      </c>
+      <c r="D2144">
+        <v>2023</v>
+      </c>
+      <c r="E2144" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2144" s="6">
+        <v>2423</v>
+      </c>
+      <c r="G2144" s="6">
+        <v>591</v>
+      </c>
+      <c r="H2144" s="6">
+        <v>2141</v>
+      </c>
+      <c r="I2144" s="6">
+        <v>5155</v>
+      </c>
+      <c r="J2144" s="2"/>
+    </row>
+    <row r="2145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2145">
+        <v>1</v>
+      </c>
+      <c r="B2145">
+        <v>2</v>
+      </c>
+      <c r="C2145">
+        <v>4</v>
+      </c>
+      <c r="D2145">
+        <v>2023</v>
+      </c>
+      <c r="E2145" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2145" s="6">
+        <v>20</v>
+      </c>
+      <c r="G2145" s="6">
+        <v>9</v>
+      </c>
+      <c r="H2145" s="6">
+        <v>56</v>
+      </c>
+      <c r="I2145" s="6">
+        <v>85</v>
+      </c>
+      <c r="J2145" s="2"/>
+    </row>
+    <row r="2146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2146">
+        <v>1</v>
+      </c>
+      <c r="B2146">
+        <v>2</v>
+      </c>
+      <c r="C2146">
+        <v>4</v>
+      </c>
+      <c r="D2146">
+        <v>2023</v>
+      </c>
+      <c r="E2146" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2146" s="6">
+        <v>3016</v>
+      </c>
+      <c r="G2146" s="6">
+        <v>922</v>
+      </c>
+      <c r="H2146" s="6">
+        <v>3781</v>
+      </c>
+      <c r="I2146" s="6">
+        <v>7719</v>
+      </c>
+      <c r="J2146" s="2"/>
+    </row>
+    <row r="2147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2147">
+        <v>1</v>
+      </c>
+      <c r="B2147">
+        <v>2</v>
+      </c>
+      <c r="C2147">
+        <v>4</v>
+      </c>
+      <c r="D2147">
+        <v>2023</v>
+      </c>
+      <c r="E2147" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2147" s="6">
+        <v>66</v>
+      </c>
+      <c r="G2147" s="6">
+        <v>21</v>
+      </c>
+      <c r="H2147" s="6">
+        <v>104</v>
+      </c>
+      <c r="I2147" s="6">
+        <v>191</v>
+      </c>
+      <c r="J2147" s="2"/>
+    </row>
+    <row r="2148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2148">
+        <v>1</v>
+      </c>
+      <c r="B2148">
+        <v>2</v>
+      </c>
+      <c r="C2148">
+        <v>4</v>
+      </c>
+      <c r="D2148">
+        <v>2023</v>
+      </c>
+      <c r="E2148" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2148" s="6">
+        <v>207</v>
+      </c>
+      <c r="G2148" s="6">
+        <v>96</v>
+      </c>
+      <c r="H2148" s="6">
+        <v>404</v>
+      </c>
+      <c r="I2148" s="6">
+        <v>707</v>
+      </c>
+      <c r="J2148" s="2"/>
+    </row>
+    <row r="2149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2149">
+        <v>1</v>
+      </c>
+      <c r="B2149">
+        <v>2</v>
+      </c>
+      <c r="C2149">
+        <v>4</v>
+      </c>
+      <c r="D2149">
+        <v>2023</v>
+      </c>
+      <c r="E2149" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2149" s="6">
+        <v>49</v>
+      </c>
+      <c r="G2149" s="6">
+        <v>35</v>
+      </c>
+      <c r="H2149" s="6">
+        <v>159</v>
+      </c>
+      <c r="I2149" s="6">
+        <v>243</v>
+      </c>
+      <c r="J2149" s="2"/>
+    </row>
+    <row r="2150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2150">
+        <v>1</v>
+      </c>
+      <c r="B2150">
+        <v>2</v>
+      </c>
+      <c r="C2150">
+        <v>4</v>
+      </c>
+      <c r="D2150">
+        <v>2023</v>
+      </c>
+      <c r="E2150" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2150" s="6">
+        <v>10</v>
+      </c>
+      <c r="G2150" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2150" s="6">
+        <v>21</v>
+      </c>
+      <c r="I2150" s="6">
+        <v>36</v>
+      </c>
+      <c r="J2150" s="2"/>
+    </row>
+    <row r="2151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2151">
+        <v>1</v>
+      </c>
+      <c r="B2151">
+        <v>2</v>
+      </c>
+      <c r="C2151">
+        <v>4</v>
+      </c>
+      <c r="D2151">
+        <v>2023</v>
+      </c>
+      <c r="E2151" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2151" s="6">
+        <v>160</v>
+      </c>
+      <c r="G2151" s="6">
+        <v>148</v>
+      </c>
+      <c r="H2151" s="6">
+        <v>477</v>
+      </c>
+      <c r="I2151" s="6">
+        <v>785</v>
+      </c>
+      <c r="J2151" s="2"/>
+    </row>
+    <row r="2152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2152">
+        <v>1</v>
+      </c>
+      <c r="B2152">
+        <v>2</v>
+      </c>
+      <c r="C2152">
+        <v>4</v>
+      </c>
+      <c r="D2152">
+        <v>2023</v>
+      </c>
+      <c r="E2152" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2152" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2152" s="6">
+        <v>6</v>
+      </c>
+      <c r="H2152" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2152" s="6">
+        <v>19</v>
+      </c>
+      <c r="J2152" s="2"/>
+    </row>
+    <row r="2153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2153">
+        <v>1</v>
+      </c>
+      <c r="B2153">
+        <v>2</v>
+      </c>
+      <c r="C2153">
+        <v>4</v>
+      </c>
+      <c r="D2153">
+        <v>2023</v>
+      </c>
+      <c r="E2153" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2153" s="6">
+        <v>95</v>
+      </c>
+      <c r="G2153" s="6">
+        <v>39</v>
+      </c>
+      <c r="H2153" s="6">
+        <v>115</v>
+      </c>
+      <c r="I2153" s="6">
+        <v>249</v>
+      </c>
+      <c r="J2153" s="2"/>
+    </row>
+    <row r="2154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2154">
+        <v>1</v>
+      </c>
+      <c r="B2154">
+        <v>2</v>
+      </c>
+      <c r="C2154">
+        <v>5</v>
+      </c>
+      <c r="D2154">
+        <v>2023</v>
+      </c>
+      <c r="E2154" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2154" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2154" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2154" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2154" s="6">
+        <v>14</v>
+      </c>
+      <c r="J2154" s="2"/>
+    </row>
+    <row r="2155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2155">
+        <v>1</v>
+      </c>
+      <c r="B2155">
+        <v>2</v>
+      </c>
+      <c r="C2155">
+        <v>5</v>
+      </c>
+      <c r="D2155">
+        <v>2023</v>
+      </c>
+      <c r="E2155" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2155" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2155" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2155" s="6">
+        <v>14</v>
+      </c>
+      <c r="I2155" s="6">
+        <v>21</v>
+      </c>
+      <c r="J2155" s="2"/>
+    </row>
+    <row r="2156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2156">
+        <v>1</v>
+      </c>
+      <c r="B2156">
+        <v>2</v>
+      </c>
+      <c r="C2156">
+        <v>5</v>
+      </c>
+      <c r="D2156">
+        <v>2023</v>
+      </c>
+      <c r="E2156" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2156" s="6">
+        <v>7</v>
+      </c>
+      <c r="G2156" s="6">
+        <v>6</v>
+      </c>
+      <c r="H2156" s="6">
+        <v>22</v>
+      </c>
+      <c r="I2156" s="6">
+        <v>35</v>
+      </c>
+      <c r="J2156" s="2"/>
+    </row>
+    <row r="2157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2157">
+        <v>1</v>
+      </c>
+      <c r="B2157">
+        <v>2</v>
+      </c>
+      <c r="C2157">
+        <v>5</v>
+      </c>
+      <c r="D2157">
+        <v>2023</v>
+      </c>
+      <c r="E2157" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2157" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2157" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2157" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2157" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2157" s="2"/>
+    </row>
+    <row r="2158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2158">
+        <v>1</v>
+      </c>
+      <c r="B2158">
+        <v>2</v>
+      </c>
+      <c r="C2158">
+        <v>5</v>
+      </c>
+      <c r="D2158">
+        <v>2023</v>
+      </c>
+      <c r="E2158" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2158" s="6">
+        <v>9</v>
+      </c>
+      <c r="G2158" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2158" s="6">
+        <v>19</v>
+      </c>
+      <c r="I2158" s="6">
+        <v>35</v>
+      </c>
+      <c r="J2158" s="2"/>
+    </row>
+    <row r="2159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2159">
+        <v>1</v>
+      </c>
+      <c r="B2159">
+        <v>2</v>
+      </c>
+      <c r="C2159">
+        <v>5</v>
+      </c>
+      <c r="D2159">
+        <v>2023</v>
+      </c>
+      <c r="E2159" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2159" s="6">
+        <v>1632</v>
+      </c>
+      <c r="G2159" s="6">
+        <v>728</v>
+      </c>
+      <c r="H2159" s="6">
+        <v>2098</v>
+      </c>
+      <c r="I2159" s="6">
+        <v>4458</v>
+      </c>
+      <c r="J2159" s="2"/>
+    </row>
+    <row r="2160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2160">
+        <v>1</v>
+      </c>
+      <c r="B2160">
+        <v>2</v>
+      </c>
+      <c r="C2160">
+        <v>5</v>
+      </c>
+      <c r="D2160">
+        <v>2023</v>
+      </c>
+      <c r="E2160" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2160" s="6">
+        <v>6</v>
+      </c>
+      <c r="G2160" s="6">
+        <v>8</v>
+      </c>
+      <c r="H2160" s="6">
+        <v>35</v>
+      </c>
+      <c r="I2160" s="6">
+        <v>49</v>
+      </c>
+      <c r="J2160" s="2"/>
+    </row>
+    <row r="2161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2161">
+        <v>1</v>
+      </c>
+      <c r="B2161">
+        <v>2</v>
+      </c>
+      <c r="C2161">
+        <v>5</v>
+      </c>
+      <c r="D2161">
+        <v>2023</v>
+      </c>
+      <c r="E2161" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2161" s="6">
+        <v>2347</v>
+      </c>
+      <c r="G2161" s="6">
+        <v>595</v>
+      </c>
+      <c r="H2161" s="6">
+        <v>2313</v>
+      </c>
+      <c r="I2161" s="6">
+        <v>5255</v>
+      </c>
+      <c r="J2161" s="2"/>
+    </row>
+    <row r="2162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2162">
+        <v>1</v>
+      </c>
+      <c r="B2162">
+        <v>2</v>
+      </c>
+      <c r="C2162">
+        <v>5</v>
+      </c>
+      <c r="D2162">
+        <v>2023</v>
+      </c>
+      <c r="E2162" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2162" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2162" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2162" s="6">
+        <v>4</v>
+      </c>
+      <c r="I2162" s="6">
+        <v>6</v>
+      </c>
+      <c r="J2162" s="2"/>
+    </row>
+    <row r="2163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2163">
+        <v>1</v>
+      </c>
+      <c r="B2163">
+        <v>2</v>
+      </c>
+      <c r="C2163">
+        <v>5</v>
+      </c>
+      <c r="D2163">
+        <v>2023</v>
+      </c>
+      <c r="E2163" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2163" s="6">
+        <v>3095</v>
+      </c>
+      <c r="G2163" s="6">
+        <v>1058</v>
+      </c>
+      <c r="H2163" s="6">
+        <v>3967</v>
+      </c>
+      <c r="I2163" s="6">
+        <v>8120</v>
+      </c>
+      <c r="J2163" s="2"/>
+    </row>
+    <row r="2164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2164">
+        <v>1</v>
+      </c>
+      <c r="B2164">
+        <v>2</v>
+      </c>
+      <c r="C2164">
+        <v>5</v>
+      </c>
+      <c r="D2164">
+        <v>2023</v>
+      </c>
+      <c r="E2164" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2164" s="6">
+        <v>54</v>
+      </c>
+      <c r="G2164" s="6">
+        <v>31</v>
+      </c>
+      <c r="H2164" s="6">
+        <v>114</v>
+      </c>
+      <c r="I2164" s="6">
+        <v>199</v>
+      </c>
+      <c r="J2164" s="2"/>
+    </row>
+    <row r="2165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2165">
+        <v>1</v>
+      </c>
+      <c r="B2165">
+        <v>2</v>
+      </c>
+      <c r="C2165">
+        <v>5</v>
+      </c>
+      <c r="D2165">
+        <v>2023</v>
+      </c>
+      <c r="E2165" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2165" s="6">
+        <v>202</v>
+      </c>
+      <c r="G2165" s="6">
+        <v>103</v>
+      </c>
+      <c r="H2165" s="6">
+        <v>441</v>
+      </c>
+      <c r="I2165" s="6">
+        <v>746</v>
+      </c>
+      <c r="J2165" s="2"/>
+    </row>
+    <row r="2166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2166">
+        <v>1</v>
+      </c>
+      <c r="B2166">
+        <v>2</v>
+      </c>
+      <c r="C2166">
+        <v>5</v>
+      </c>
+      <c r="D2166">
+        <v>2023</v>
+      </c>
+      <c r="E2166" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2166" s="6">
+        <v>69</v>
+      </c>
+      <c r="G2166" s="6">
+        <v>47</v>
+      </c>
+      <c r="H2166" s="6">
+        <v>149</v>
+      </c>
+      <c r="I2166" s="6">
+        <v>265</v>
+      </c>
+      <c r="J2166" s="2"/>
+    </row>
+    <row r="2167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2167">
+        <v>1</v>
+      </c>
+      <c r="B2167">
+        <v>2</v>
+      </c>
+      <c r="C2167">
+        <v>5</v>
+      </c>
+      <c r="D2167">
+        <v>2023</v>
+      </c>
+      <c r="E2167" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2167" s="6">
+        <v>7</v>
+      </c>
+      <c r="G2167" s="6">
+        <v>9</v>
+      </c>
+      <c r="H2167" s="6">
+        <v>27</v>
+      </c>
+      <c r="I2167" s="6">
+        <v>43</v>
+      </c>
+      <c r="J2167" s="2"/>
+    </row>
+    <row r="2168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2168">
+        <v>1</v>
+      </c>
+      <c r="B2168">
+        <v>2</v>
+      </c>
+      <c r="C2168">
+        <v>5</v>
+      </c>
+      <c r="D2168">
+        <v>2023</v>
+      </c>
+      <c r="E2168" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2168" s="6">
+        <v>168</v>
+      </c>
+      <c r="G2168" s="6">
+        <v>182</v>
+      </c>
+      <c r="H2168" s="6">
+        <v>570</v>
+      </c>
+      <c r="I2168" s="6">
+        <v>920</v>
+      </c>
+      <c r="J2168" s="2"/>
+    </row>
+    <row r="2169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2169">
+        <v>1</v>
+      </c>
+      <c r="B2169">
+        <v>2</v>
+      </c>
+      <c r="C2169">
+        <v>5</v>
+      </c>
+      <c r="D2169">
+        <v>2023</v>
+      </c>
+      <c r="E2169" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2169" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2169" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2169" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2169" s="6">
+        <v>13</v>
+      </c>
+      <c r="J2169" s="2"/>
+    </row>
+    <row r="2170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2170">
+        <v>1</v>
+      </c>
+      <c r="B2170">
+        <v>2</v>
+      </c>
+      <c r="C2170">
+        <v>5</v>
+      </c>
+      <c r="D2170">
+        <v>2023</v>
+      </c>
+      <c r="E2170" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2170" s="6">
+        <v>35</v>
+      </c>
+      <c r="G2170" s="6">
+        <v>12</v>
+      </c>
+      <c r="H2170" s="6">
+        <v>31</v>
+      </c>
+      <c r="I2170" s="6">
+        <v>78</v>
+      </c>
+      <c r="J2170" s="2"/>
+    </row>
+    <row r="2171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2171">
+        <v>1</v>
+      </c>
+      <c r="B2171">
+        <v>2</v>
+      </c>
+      <c r="C2171">
+        <v>6</v>
+      </c>
+      <c r="D2171">
+        <v>2023</v>
+      </c>
+      <c r="E2171" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2171" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2171" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2171" s="6">
+        <v>16</v>
+      </c>
+      <c r="I2171" s="6">
+        <v>19</v>
+      </c>
+      <c r="J2171" s="2"/>
+    </row>
+    <row r="2172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2172">
+        <v>1</v>
+      </c>
+      <c r="B2172">
+        <v>2</v>
+      </c>
+      <c r="C2172">
+        <v>6</v>
+      </c>
+      <c r="D2172">
+        <v>2023</v>
+      </c>
+      <c r="E2172" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2172" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2172" s="6">
+        <v>4</v>
+      </c>
+      <c r="H2172" s="6">
+        <v>5</v>
+      </c>
+      <c r="I2172" s="6">
+        <v>10</v>
+      </c>
+      <c r="J2172" s="2"/>
+    </row>
+    <row r="2173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2173">
+        <v>1</v>
+      </c>
+      <c r="B2173">
+        <v>2</v>
+      </c>
+      <c r="C2173">
+        <v>6</v>
+      </c>
+      <c r="D2173">
+        <v>2023</v>
+      </c>
+      <c r="E2173" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2173" s="6">
+        <v>3</v>
+      </c>
+      <c r="G2173" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2173" s="6">
+        <v>21</v>
+      </c>
+      <c r="I2173" s="6">
+        <v>29</v>
+      </c>
+      <c r="J2173" s="2"/>
+    </row>
+    <row r="2174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2174">
+        <v>1</v>
+      </c>
+      <c r="B2174">
+        <v>2</v>
+      </c>
+      <c r="C2174">
+        <v>6</v>
+      </c>
+      <c r="D2174">
+        <v>2023</v>
+      </c>
+      <c r="E2174" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2174" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2174" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2174" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2174" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2174" s="2"/>
+    </row>
+    <row r="2175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2175">
+        <v>1</v>
+      </c>
+      <c r="B2175">
+        <v>2</v>
+      </c>
+      <c r="C2175">
+        <v>6</v>
+      </c>
+      <c r="D2175">
+        <v>2023</v>
+      </c>
+      <c r="E2175" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2175" s="6">
+        <v>8</v>
+      </c>
+      <c r="G2175" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2175" s="6">
+        <v>17</v>
+      </c>
+      <c r="I2175" s="6">
+        <v>30</v>
+      </c>
+      <c r="J2175" s="2"/>
+    </row>
+    <row r="2176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2176">
+        <v>1</v>
+      </c>
+      <c r="B2176">
+        <v>2</v>
+      </c>
+      <c r="C2176">
+        <v>6</v>
+      </c>
+      <c r="D2176">
+        <v>2023</v>
+      </c>
+      <c r="E2176" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2176" s="6">
+        <v>1688</v>
+      </c>
+      <c r="G2176" s="6">
+        <v>655</v>
+      </c>
+      <c r="H2176" s="6">
+        <v>1829</v>
+      </c>
+      <c r="I2176" s="6">
+        <v>4172</v>
+      </c>
+      <c r="J2176" s="2"/>
+    </row>
+    <row r="2177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2177">
+        <v>1</v>
+      </c>
+      <c r="B2177">
+        <v>2</v>
+      </c>
+      <c r="C2177">
+        <v>6</v>
+      </c>
+      <c r="D2177">
+        <v>2023</v>
+      </c>
+      <c r="E2177" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2177" s="6">
+        <v>12</v>
+      </c>
+      <c r="G2177" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2177" s="6">
+        <v>25</v>
+      </c>
+      <c r="I2177" s="6">
+        <v>42</v>
+      </c>
+      <c r="J2177" s="2"/>
+    </row>
+    <row r="2178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2178">
+        <v>1</v>
+      </c>
+      <c r="B2178">
+        <v>2</v>
+      </c>
+      <c r="C2178">
+        <v>6</v>
+      </c>
+      <c r="D2178">
+        <v>2023</v>
+      </c>
+      <c r="E2178" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2178" s="6">
+        <v>2342</v>
+      </c>
+      <c r="G2178" s="6">
+        <v>459</v>
+      </c>
+      <c r="H2178" s="6">
+        <v>2033</v>
+      </c>
+      <c r="I2178" s="6">
+        <v>4834</v>
+      </c>
+      <c r="J2178" s="2"/>
+    </row>
+    <row r="2179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2179">
+        <v>1</v>
+      </c>
+      <c r="B2179">
+        <v>2</v>
+      </c>
+      <c r="C2179">
+        <v>6</v>
+      </c>
+      <c r="D2179">
+        <v>2023</v>
+      </c>
+      <c r="E2179" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2179" s="6">
+        <v>7</v>
+      </c>
+      <c r="G2179" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2179" s="6">
+        <v>8</v>
+      </c>
+      <c r="I2179" s="6">
+        <v>17</v>
+      </c>
+      <c r="J2179" s="2"/>
+    </row>
+    <row r="2180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2180">
+        <v>1</v>
+      </c>
+      <c r="B2180">
+        <v>2</v>
+      </c>
+      <c r="C2180">
+        <v>6</v>
+      </c>
+      <c r="D2180">
+        <v>2023</v>
+      </c>
+      <c r="E2180" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2180" s="6">
+        <v>3009</v>
+      </c>
+      <c r="G2180" s="6">
+        <v>823</v>
+      </c>
+      <c r="H2180" s="6">
+        <v>3526</v>
+      </c>
+      <c r="I2180" s="6">
+        <v>7358</v>
+      </c>
+      <c r="J2180" s="2"/>
+    </row>
+    <row r="2181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2181">
+        <v>1</v>
+      </c>
+      <c r="B2181">
+        <v>2</v>
+      </c>
+      <c r="C2181">
+        <v>6</v>
+      </c>
+      <c r="D2181">
+        <v>2023</v>
+      </c>
+      <c r="E2181" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2181" s="6">
+        <v>46</v>
+      </c>
+      <c r="G2181" s="6">
+        <v>19</v>
+      </c>
+      <c r="H2181" s="6">
+        <v>105</v>
+      </c>
+      <c r="I2181" s="6">
+        <v>170</v>
+      </c>
+      <c r="J2181" s="2"/>
+    </row>
+    <row r="2182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2182">
+        <v>1</v>
+      </c>
+      <c r="B2182">
+        <v>2</v>
+      </c>
+      <c r="C2182">
+        <v>6</v>
+      </c>
+      <c r="D2182">
+        <v>2023</v>
+      </c>
+      <c r="E2182" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2182" s="6">
+        <v>204</v>
+      </c>
+      <c r="G2182" s="6">
+        <v>85</v>
+      </c>
+      <c r="H2182" s="6">
+        <v>410</v>
+      </c>
+      <c r="I2182" s="6">
+        <v>699</v>
+      </c>
+      <c r="J2182" s="2"/>
+    </row>
+    <row r="2183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2183">
+        <v>1</v>
+      </c>
+      <c r="B2183">
+        <v>2</v>
+      </c>
+      <c r="C2183">
+        <v>6</v>
+      </c>
+      <c r="D2183">
+        <v>2023</v>
+      </c>
+      <c r="E2183" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2183" s="6">
+        <v>49</v>
+      </c>
+      <c r="G2183" s="6">
+        <v>43</v>
+      </c>
+      <c r="H2183" s="6">
+        <v>142</v>
+      </c>
+      <c r="I2183" s="6">
+        <v>234</v>
+      </c>
+      <c r="J2183" s="2"/>
+    </row>
+    <row r="2184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2184">
+        <v>1</v>
+      </c>
+      <c r="B2184">
+        <v>2</v>
+      </c>
+      <c r="C2184">
+        <v>6</v>
+      </c>
+      <c r="D2184">
+        <v>2023</v>
+      </c>
+      <c r="E2184" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2184" s="6">
+        <v>10</v>
+      </c>
+      <c r="G2184" s="6">
+        <v>4</v>
+      </c>
+      <c r="H2184" s="6">
+        <v>19</v>
+      </c>
+      <c r="I2184" s="6">
+        <v>33</v>
+      </c>
+      <c r="J2184" s="2"/>
+    </row>
+    <row r="2185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2185">
+        <v>1</v>
+      </c>
+      <c r="B2185">
+        <v>2</v>
+      </c>
+      <c r="C2185">
+        <v>6</v>
+      </c>
+      <c r="D2185">
+        <v>2023</v>
+      </c>
+      <c r="E2185" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2185" s="6">
+        <v>160</v>
+      </c>
+      <c r="G2185" s="6">
+        <v>177</v>
+      </c>
+      <c r="H2185" s="6">
+        <v>442</v>
+      </c>
+      <c r="I2185" s="6">
+        <v>779</v>
+      </c>
+      <c r="J2185" s="2"/>
+    </row>
+    <row r="2186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2186">
+        <v>1</v>
+      </c>
+      <c r="B2186">
+        <v>2</v>
+      </c>
+      <c r="C2186">
+        <v>6</v>
+      </c>
+      <c r="D2186">
+        <v>2023</v>
+      </c>
+      <c r="E2186" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2186" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2186" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2186" s="6">
+        <v>10</v>
+      </c>
+      <c r="I2186" s="6">
+        <v>11</v>
+      </c>
+      <c r="J2186" s="2"/>
+    </row>
+    <row r="2187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2187">
+        <v>1</v>
+      </c>
+      <c r="B2187">
+        <v>2</v>
+      </c>
+      <c r="C2187">
+        <v>6</v>
+      </c>
+      <c r="D2187">
+        <v>2023</v>
+      </c>
+      <c r="E2187" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2187" s="6">
+        <v>34</v>
+      </c>
+      <c r="G2187" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2187" s="6">
+        <v>26</v>
+      </c>
+      <c r="I2187" s="6">
+        <v>65</v>
+      </c>
+      <c r="J2187" s="2"/>
+    </row>
+    <row r="2188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2188">
+        <v>2</v>
+      </c>
+      <c r="B2188">
+        <v>3</v>
+      </c>
+      <c r="C2188">
+        <v>7</v>
+      </c>
+      <c r="D2188">
+        <v>2023</v>
+      </c>
+      <c r="E2188" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2188" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2188" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2188" s="6">
+        <v>7</v>
+      </c>
+      <c r="I2188" s="6">
+        <v>11</v>
+      </c>
+      <c r="J2188" s="2"/>
+    </row>
+    <row r="2189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2189">
+        <v>2</v>
+      </c>
+      <c r="B2189">
+        <v>3</v>
+      </c>
+      <c r="C2189">
+        <v>7</v>
+      </c>
+      <c r="D2189">
+        <v>2023</v>
+      </c>
+      <c r="E2189" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2189" s="6">
+        <v>3</v>
+      </c>
+      <c r="G2189" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2189" s="6">
+        <v>7</v>
+      </c>
+      <c r="I2189" s="6">
+        <v>12</v>
+      </c>
+      <c r="J2189" s="2"/>
+    </row>
+    <row r="2190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2190">
+        <v>2</v>
+      </c>
+      <c r="B2190">
+        <v>3</v>
+      </c>
+      <c r="C2190">
+        <v>7</v>
+      </c>
+      <c r="D2190">
+        <v>2023</v>
+      </c>
+      <c r="E2190" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2190" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2190" s="6">
+        <v>4</v>
+      </c>
+      <c r="H2190" s="6">
+        <v>14</v>
+      </c>
+      <c r="I2190" s="6">
+        <v>23</v>
+      </c>
+      <c r="J2190" s="2"/>
+    </row>
+    <row r="2191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2191">
+        <v>2</v>
+      </c>
+      <c r="B2191">
+        <v>3</v>
+      </c>
+      <c r="C2191">
+        <v>7</v>
+      </c>
+      <c r="D2191">
+        <v>2023</v>
+      </c>
+      <c r="E2191" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2191" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2191" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2191" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2191" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2191" s="2"/>
+    </row>
+    <row r="2192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2192">
+        <v>2</v>
+      </c>
+      <c r="B2192">
+        <v>3</v>
+      </c>
+      <c r="C2192">
+        <v>7</v>
+      </c>
+      <c r="D2192">
+        <v>2023</v>
+      </c>
+      <c r="E2192" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2192" s="6">
+        <v>12</v>
+      </c>
+      <c r="G2192" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2192" s="6">
+        <v>19</v>
+      </c>
+      <c r="I2192" s="6">
+        <v>36</v>
+      </c>
+      <c r="J2192" s="2"/>
+    </row>
+    <row r="2193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2193">
+        <v>2</v>
+      </c>
+      <c r="B2193">
+        <v>3</v>
+      </c>
+      <c r="C2193">
+        <v>7</v>
+      </c>
+      <c r="D2193">
+        <v>2023</v>
+      </c>
+      <c r="E2193" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2193" s="6">
+        <v>1814</v>
+      </c>
+      <c r="G2193" s="6">
+        <v>671</v>
+      </c>
+      <c r="H2193" s="6">
+        <v>2164</v>
+      </c>
+      <c r="I2193" s="6">
+        <v>4649</v>
+      </c>
+      <c r="J2193" s="2"/>
+    </row>
+    <row r="2194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2194">
+        <v>2</v>
+      </c>
+      <c r="B2194">
+        <v>3</v>
+      </c>
+      <c r="C2194">
+        <v>7</v>
+      </c>
+      <c r="D2194">
+        <v>2023</v>
+      </c>
+      <c r="E2194" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2194" s="6">
+        <v>13</v>
+      </c>
+      <c r="G2194" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2194" s="6">
+        <v>30</v>
+      </c>
+      <c r="I2194" s="6">
+        <v>46</v>
+      </c>
+      <c r="J2194" s="2"/>
+    </row>
+    <row r="2195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2195">
+        <v>2</v>
+      </c>
+      <c r="B2195">
+        <v>3</v>
+      </c>
+      <c r="C2195">
+        <v>7</v>
+      </c>
+      <c r="D2195">
+        <v>2023</v>
+      </c>
+      <c r="E2195" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2195" s="6">
+        <v>2454</v>
+      </c>
+      <c r="G2195" s="6">
+        <v>559</v>
+      </c>
+      <c r="H2195" s="6">
+        <v>2497</v>
+      </c>
+      <c r="I2195" s="6">
+        <v>5510</v>
+      </c>
+      <c r="J2195" s="2"/>
+    </row>
+    <row r="2196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2196">
+        <v>2</v>
+      </c>
+      <c r="B2196">
+        <v>3</v>
+      </c>
+      <c r="C2196">
+        <v>7</v>
+      </c>
+      <c r="D2196">
+        <v>2023</v>
+      </c>
+      <c r="E2196" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2196" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2196" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2196" s="6">
+        <v>5</v>
+      </c>
+      <c r="I2196" s="6">
+        <v>9</v>
+      </c>
+      <c r="J2196" s="2"/>
+    </row>
+    <row r="2197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2197">
+        <v>2</v>
+      </c>
+      <c r="B2197">
+        <v>3</v>
+      </c>
+      <c r="C2197">
+        <v>7</v>
+      </c>
+      <c r="D2197">
+        <v>2023</v>
+      </c>
+      <c r="E2197" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2197" s="6">
+        <v>3087</v>
+      </c>
+      <c r="G2197" s="6">
+        <v>931</v>
+      </c>
+      <c r="H2197" s="6">
+        <v>3797</v>
+      </c>
+      <c r="I2197" s="6">
+        <v>7815</v>
+      </c>
+      <c r="J2197" s="2"/>
+    </row>
+    <row r="2198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2198">
+        <v>2</v>
+      </c>
+      <c r="B2198">
+        <v>3</v>
+      </c>
+      <c r="C2198">
+        <v>7</v>
+      </c>
+      <c r="D2198">
+        <v>2023</v>
+      </c>
+      <c r="E2198" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2198" s="6">
+        <v>67</v>
+      </c>
+      <c r="G2198" s="6">
+        <v>25</v>
+      </c>
+      <c r="H2198" s="6">
+        <v>123</v>
+      </c>
+      <c r="I2198" s="6">
+        <v>215</v>
+      </c>
+      <c r="J2198" s="2"/>
+    </row>
+    <row r="2199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2199">
+        <v>2</v>
+      </c>
+      <c r="B2199">
+        <v>3</v>
+      </c>
+      <c r="C2199">
+        <v>7</v>
+      </c>
+      <c r="D2199">
+        <v>2023</v>
+      </c>
+      <c r="E2199" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2199" s="6">
+        <v>220</v>
+      </c>
+      <c r="G2199" s="6">
+        <v>111</v>
+      </c>
+      <c r="H2199" s="6">
+        <v>419</v>
+      </c>
+      <c r="I2199" s="6">
+        <v>750</v>
+      </c>
+      <c r="J2199" s="2"/>
+    </row>
+    <row r="2200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2200">
+        <v>2</v>
+      </c>
+      <c r="B2200">
+        <v>3</v>
+      </c>
+      <c r="C2200">
+        <v>7</v>
+      </c>
+      <c r="D2200">
+        <v>2023</v>
+      </c>
+      <c r="E2200" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2200" s="6">
+        <v>52</v>
+      </c>
+      <c r="G2200" s="6">
+        <v>33</v>
+      </c>
+      <c r="H2200" s="6">
+        <v>136</v>
+      </c>
+      <c r="I2200" s="6">
+        <v>221</v>
+      </c>
+      <c r="J2200" s="2"/>
+    </row>
+    <row r="2201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2201">
+        <v>2</v>
+      </c>
+      <c r="B2201">
+        <v>3</v>
+      </c>
+      <c r="C2201">
+        <v>7</v>
+      </c>
+      <c r="D2201">
+        <v>2023</v>
+      </c>
+      <c r="E2201" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2201" s="6">
+        <v>6</v>
+      </c>
+      <c r="G2201" s="6">
+        <v>3</v>
+      </c>
+      <c r="H2201" s="6">
+        <v>25</v>
+      </c>
+      <c r="I2201" s="6">
+        <v>34</v>
+      </c>
+      <c r="J2201" s="2"/>
+    </row>
+    <row r="2202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2202">
+        <v>2</v>
+      </c>
+      <c r="B2202">
+        <v>3</v>
+      </c>
+      <c r="C2202">
+        <v>7</v>
+      </c>
+      <c r="D2202">
+        <v>2023</v>
+      </c>
+      <c r="E2202" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2202" s="6">
+        <v>130</v>
+      </c>
+      <c r="G2202" s="6">
+        <v>151</v>
+      </c>
+      <c r="H2202" s="6">
+        <v>444</v>
+      </c>
+      <c r="I2202" s="6">
+        <v>725</v>
+      </c>
+      <c r="J2202" s="2"/>
+    </row>
+    <row r="2203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2203">
+        <v>2</v>
+      </c>
+      <c r="B2203">
+        <v>3</v>
+      </c>
+      <c r="C2203">
+        <v>7</v>
+      </c>
+      <c r="D2203">
+        <v>2023</v>
+      </c>
+      <c r="E2203" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2203" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2203" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2203" s="6">
+        <v>13</v>
+      </c>
+      <c r="I2203" s="6">
+        <v>14</v>
+      </c>
+      <c r="J2203" s="2"/>
+    </row>
+    <row r="2204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2204">
+        <v>2</v>
+      </c>
+      <c r="B2204">
+        <v>3</v>
+      </c>
+      <c r="C2204">
+        <v>7</v>
+      </c>
+      <c r="D2204">
+        <v>2023</v>
+      </c>
+      <c r="E2204" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2204" s="6">
+        <v>32</v>
+      </c>
+      <c r="G2204" s="6">
+        <v>7</v>
+      </c>
+      <c r="H2204" s="6">
+        <v>38</v>
+      </c>
+      <c r="I2204" s="6">
+        <v>77</v>
+      </c>
+      <c r="J2204" s="2"/>
+    </row>
+    <row r="2205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E2205" s="5"/>
+      <c r="F2205" s="5"/>
+      <c r="G2205" s="5"/>
+      <c r="H2205" s="5"/>
+      <c r="I2205" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1983">
-    <sortState ref="A2:I1983">
+  <autoFilter ref="A1:I1983" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I1983">
       <sortCondition ref="D1:D1983"/>
     </sortState>
   </autoFilter>
